--- a/VerveStacks_GHA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_GHA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01675D97-11EA-42F6-AAF8-1F859CBC4EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EA064FD-F541-422D-B356-EC97DD62AFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="139">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -304,6 +304,114 @@
     <t>indesc</t>
   </si>
   <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
+  </si>
+  <si>
+    <t>w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>w201845280-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w201845280-765_IND</t>
+  </si>
+  <si>
+    <t>w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>w420797421-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w420797421-765_IND</t>
+  </si>
+  <si>
+    <t>w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>IN684-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - IN684-765_IND</t>
+  </si>
+  <si>
+    <t>w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
+  </si>
+  <si>
+    <t>w203673991-400_IND</t>
+  </si>
+  <si>
+    <t>at grid node - w203673991-400_IND</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>-*cofiring*</t>
+  </si>
+  <si>
+    <t>-EFF</t>
+  </si>
+  <si>
+    <t>en_biomass_cofiring*,en_geothermal*</t>
+  </si>
+  <si>
     <t>GHA</t>
   </si>
   <si>
@@ -313,18 +421,12 @@
     <t>at grid node - w672526714-330_GHA</t>
   </si>
   <si>
-    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
-  </si>
-  <si>
     <t>w282578857-330_GHA</t>
   </si>
   <si>
     <t>at grid node - w282578857-330_GHA</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
-  </si>
-  <si>
     <t>r15772152-330_GHA</t>
   </si>
   <si>
@@ -353,9 +455,6 @@
   </si>
   <si>
     <t>at grid node - w930744195-225_GHA</t>
-  </si>
-  <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
 </sst>
 </file>
@@ -683,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:O17"/>
+  <dimension ref="B3:O26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.45">
@@ -758,208 +857,598 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
         <v>89</v>
       </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
       <c r="G11" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="N11" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="O11" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" t="s">
+        <v>124</v>
+      </c>
+      <c r="M12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12" t="s">
+        <v>126</v>
+      </c>
+      <c r="O12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
         <v>88</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" t="s">
+        <v>124</v>
+      </c>
+      <c r="M13" t="s">
+        <v>135</v>
+      </c>
+      <c r="N13" t="s">
+        <v>136</v>
+      </c>
+      <c r="O13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
         <v>92</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>93</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" t="s">
+        <v>124</v>
+      </c>
+      <c r="M14" t="s">
+        <v>137</v>
+      </c>
+      <c r="N14" t="s">
+        <v>138</v>
+      </c>
+      <c r="O14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" t="s">
+        <v>116</v>
+      </c>
+      <c r="L15" t="s">
+        <v>124</v>
+      </c>
+      <c r="M15" t="s">
+        <v>131</v>
+      </c>
+      <c r="N15" t="s">
+        <v>132</v>
+      </c>
+      <c r="O15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I16" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" t="s">
+        <v>116</v>
+      </c>
+      <c r="L16" t="s">
+        <v>124</v>
+      </c>
+      <c r="M16" t="s">
+        <v>133</v>
+      </c>
+      <c r="N16" t="s">
+        <v>134</v>
+      </c>
+      <c r="O16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I17" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" t="s">
+        <v>124</v>
+      </c>
+      <c r="M17" t="s">
+        <v>129</v>
+      </c>
+      <c r="N17" t="s">
+        <v>130</v>
+      </c>
+      <c r="O17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" t="s">
+        <v>116</v>
+      </c>
+      <c r="L18" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" t="s">
+        <v>97</v>
+      </c>
+      <c r="O18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" t="s">
+        <v>116</v>
+      </c>
+      <c r="L19" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" t="s">
+        <v>108</v>
+      </c>
+      <c r="N19" t="s">
+        <v>109</v>
+      </c>
+      <c r="O19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" t="s">
+        <v>116</v>
+      </c>
+      <c r="L20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" t="s">
+        <v>90</v>
+      </c>
+      <c r="N20" t="s">
         <v>91</v>
       </c>
-      <c r="G12" t="s">
+      <c r="O20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
         <v>88</v>
       </c>
-      <c r="H12" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" t="s">
         <v>88</v>
       </c>
-      <c r="M12" t="s">
+      <c r="H21" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" t="s">
+        <v>116</v>
+      </c>
+      <c r="L21" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" t="s">
+        <v>98</v>
+      </c>
+      <c r="N21" t="s">
+        <v>99</v>
+      </c>
+      <c r="O21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
         <v>89</v>
       </c>
-      <c r="N12" t="s">
-        <v>90</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="G22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" t="s">
+        <v>116</v>
+      </c>
+      <c r="L22" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" t="s">
+        <v>106</v>
+      </c>
+      <c r="N22" t="s">
+        <v>107</v>
+      </c>
+      <c r="O22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" t="s">
+        <v>116</v>
+      </c>
+      <c r="L23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="G13" t="s">
+      <c r="O23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
         <v>88</v>
       </c>
-      <c r="H13" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" t="s">
-        <v>94</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" t="s">
         <v>88</v>
       </c>
-      <c r="M13" t="s">
-        <v>101</v>
-      </c>
-      <c r="N13" t="s">
-        <v>102</v>
-      </c>
-      <c r="O13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="G14" t="s">
+      <c r="H24" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" t="s">
+        <v>113</v>
+      </c>
+      <c r="J24" t="s">
+        <v>116</v>
+      </c>
+      <c r="L24" t="s">
         <v>88</v>
       </c>
-      <c r="H14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" t="s">
-        <v>94</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="M24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N24" t="s">
+        <v>111</v>
+      </c>
+      <c r="O24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
         <v>88</v>
       </c>
-      <c r="M14" t="s">
-        <v>103</v>
-      </c>
-      <c r="N14" t="s">
-        <v>104</v>
-      </c>
-      <c r="O14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="G15" t="s">
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" t="s">
         <v>88</v>
       </c>
-      <c r="H15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I15" t="s">
-        <v>100</v>
-      </c>
-      <c r="J15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="H25" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" t="s">
+        <v>115</v>
+      </c>
+      <c r="J25" t="s">
+        <v>116</v>
+      </c>
+      <c r="L25" t="s">
         <v>88</v>
       </c>
-      <c r="M15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N15" t="s">
-        <v>98</v>
-      </c>
-      <c r="O15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="G16" t="s">
+      <c r="M25" t="s">
+        <v>112</v>
+      </c>
+      <c r="N25" t="s">
+        <v>113</v>
+      </c>
+      <c r="O25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G26" t="s">
         <v>88</v>
       </c>
-      <c r="H16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" t="s">
-        <v>102</v>
-      </c>
-      <c r="J16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="H26" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" t="s">
+        <v>118</v>
+      </c>
+      <c r="J26" t="s">
+        <v>116</v>
+      </c>
+      <c r="L26" t="s">
         <v>88</v>
       </c>
-      <c r="M16" t="s">
-        <v>99</v>
-      </c>
-      <c r="N16" t="s">
-        <v>100</v>
-      </c>
-      <c r="O16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L17" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" t="s">
-        <v>95</v>
-      </c>
-      <c r="N17" t="s">
-        <v>96</v>
-      </c>
-      <c r="O17" t="s">
-        <v>105</v>
+      <c r="M26" t="s">
+        <v>117</v>
+      </c>
+      <c r="N26" t="s">
+        <v>118</v>
+      </c>
+      <c r="O26" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2185,6 +2674,9 @@
       <c r="G28" t="s">
         <v>5</v>
       </c>
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
@@ -2207,6 +2699,9 @@
       <c r="G30" s="1">
         <v>1</v>
       </c>
+      <c r="H30" s="3" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C31" t="s">
@@ -2364,6 +2859,9 @@
         <v>66</v>
       </c>
       <c r="F49" t="s">
+        <v>120</v>
+      </c>
+      <c r="G49" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2377,7 +2875,10 @@
       <c r="E50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G50" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2391,8 +2892,19 @@
       <c r="E51" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52">
+        <v>2100</v>
+      </c>
+      <c r="F52" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">

--- a/VerveStacks_GHA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_GHA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EA064FD-F541-422D-B356-EC97DD62AFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53DC7458-ED8A-40AD-8D1B-B9B7F5ABCFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
